--- a/fisa_accesorii_demo.xlsx
+++ b/fisa_accesorii_demo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7B6E176-1D42-4339-95D8-7B36809E57A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CB1436-86AB-40D3-9F3C-121CE2025EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$E$65</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Sheet1!$A$1:$E$90</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -806,7 +806,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A2:E65"/>
+  <dimension ref="A2:E90"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -1351,7 +1351,7 @@
       <c r="D61" s="1"/>
       <c r="E61" s="2"/>
     </row>
-    <row r="62" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="7">
         <v>57</v>
       </c>
@@ -1360,31 +1360,256 @@
       <c r="D62" s="3"/>
       <c r="E62" s="4"/>
     </row>
-    <row r="63" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="11" t="s">
+    <row r="63" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="7">
+        <v>58</v>
+      </c>
+      <c r="B63" s="2"/>
+      <c r="C63" s="16"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="2"/>
+    </row>
+    <row r="64" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="8">
+        <v>59</v>
+      </c>
+      <c r="B64" s="4"/>
+      <c r="C64" s="15"/>
+      <c r="D64" s="3"/>
+      <c r="E64" s="4"/>
+    </row>
+    <row r="65" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="7">
+        <v>60</v>
+      </c>
+      <c r="B65" s="2"/>
+      <c r="C65" s="16"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="2"/>
+    </row>
+    <row r="66" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="8">
+        <v>61</v>
+      </c>
+      <c r="B66" s="4"/>
+      <c r="C66" s="15"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="4"/>
+    </row>
+    <row r="67" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="7">
+        <v>62</v>
+      </c>
+      <c r="B67" s="2"/>
+      <c r="C67" s="16"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="2"/>
+    </row>
+    <row r="68" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="8">
+        <v>63</v>
+      </c>
+      <c r="B68" s="4"/>
+      <c r="C68" s="15"/>
+      <c r="D68" s="3"/>
+      <c r="E68" s="4"/>
+    </row>
+    <row r="69" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="7">
+        <v>64</v>
+      </c>
+      <c r="B69" s="2"/>
+      <c r="C69" s="16"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="2"/>
+    </row>
+    <row r="70" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="7">
+        <v>65</v>
+      </c>
+      <c r="B70" s="4"/>
+      <c r="C70" s="15"/>
+      <c r="D70" s="3"/>
+      <c r="E70" s="4"/>
+    </row>
+    <row r="71" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="8">
+        <v>66</v>
+      </c>
+      <c r="B71" s="2"/>
+      <c r="C71" s="16"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="2"/>
+    </row>
+    <row r="72" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="7">
+        <v>67</v>
+      </c>
+      <c r="B72" s="4"/>
+      <c r="C72" s="15"/>
+      <c r="D72" s="3"/>
+      <c r="E72" s="4"/>
+    </row>
+    <row r="73" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="8">
+        <v>68</v>
+      </c>
+      <c r="B73" s="2"/>
+      <c r="C73" s="16"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="2"/>
+    </row>
+    <row r="74" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="7">
+        <v>69</v>
+      </c>
+      <c r="B74" s="4"/>
+      <c r="C74" s="15"/>
+      <c r="D74" s="3"/>
+      <c r="E74" s="4"/>
+    </row>
+    <row r="75" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="8">
+        <v>70</v>
+      </c>
+      <c r="B75" s="2"/>
+      <c r="C75" s="16"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="2"/>
+    </row>
+    <row r="76" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="7">
+        <v>71</v>
+      </c>
+      <c r="B76" s="4"/>
+      <c r="C76" s="15"/>
+      <c r="D76" s="3"/>
+      <c r="E76" s="4"/>
+    </row>
+    <row r="77" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="7">
+        <v>72</v>
+      </c>
+      <c r="B77" s="2"/>
+      <c r="C77" s="16"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="2"/>
+    </row>
+    <row r="78" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="8">
+        <v>73</v>
+      </c>
+      <c r="B78" s="4"/>
+      <c r="C78" s="15"/>
+      <c r="D78" s="3"/>
+      <c r="E78" s="4"/>
+    </row>
+    <row r="79" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="7">
+        <v>74</v>
+      </c>
+      <c r="B79" s="2"/>
+      <c r="C79" s="16"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="2"/>
+    </row>
+    <row r="80" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="8">
+        <v>75</v>
+      </c>
+      <c r="B80" s="4"/>
+      <c r="C80" s="15"/>
+      <c r="D80" s="3"/>
+      <c r="E80" s="4"/>
+    </row>
+    <row r="81" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="7">
+        <v>76</v>
+      </c>
+      <c r="B81" s="2"/>
+      <c r="C81" s="16"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="2"/>
+    </row>
+    <row r="82" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="8">
+        <v>77</v>
+      </c>
+      <c r="B82" s="4"/>
+      <c r="C82" s="15"/>
+      <c r="D82" s="3"/>
+      <c r="E82" s="4"/>
+    </row>
+    <row r="83" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="7">
+        <v>78</v>
+      </c>
+      <c r="B83" s="2"/>
+      <c r="C83" s="16"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="2"/>
+    </row>
+    <row r="84" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="7">
+        <v>79</v>
+      </c>
+      <c r="B84" s="4"/>
+      <c r="C84" s="15"/>
+      <c r="D84" s="3"/>
+      <c r="E84" s="4"/>
+    </row>
+    <row r="85" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="8">
+        <v>80</v>
+      </c>
+      <c r="B85" s="2"/>
+      <c r="C85" s="16"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="2"/>
+    </row>
+    <row r="86" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="7">
+        <v>81</v>
+      </c>
+      <c r="B86" s="4"/>
+      <c r="C86" s="15"/>
+      <c r="D86" s="3"/>
+      <c r="E86" s="4"/>
+    </row>
+    <row r="87" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="8">
+        <v>82</v>
+      </c>
+      <c r="B87" s="2"/>
+      <c r="C87" s="16"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="2"/>
+    </row>
+    <row r="88" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A88" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="B63" s="11"/>
-      <c r="C63" s="22"/>
-      <c r="D63" s="23"/>
-      <c r="E63" s="24"/>
-    </row>
-    <row r="64" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="5" t="s">
+      <c r="B88" s="11"/>
+      <c r="C88" s="22"/>
+      <c r="D88" s="23"/>
+      <c r="E88" s="24"/>
+    </row>
+    <row r="89" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B64" s="6"/>
-      <c r="C64" s="25"/>
-      <c r="D64" s="26"/>
-      <c r="E64" s="27"/>
-    </row>
-    <row r="65" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+      <c r="B89" s="6"/>
+      <c r="C89" s="25"/>
+      <c r="D89" s="26"/>
+      <c r="E89" s="27"/>
+    </row>
+    <row r="90" spans="1:5" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C63:E64"/>
+    <mergeCell ref="C88:E89"/>
     <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.19685039370078741" bottom="0.19685039370078741" header="0.31496062992125978" footer="0.31496062992125978"/>

--- a/fisa_accesorii_demo.xlsx
+++ b/fisa_accesorii_demo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\liviu.spridon\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CB1436-86AB-40D3-9F3C-121CE2025EEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B6B6678-D9D4-4F1E-8642-F3393954635D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1361,7 +1361,7 @@
       <c r="E62" s="4"/>
     </row>
     <row r="63" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="7">
+      <c r="A63" s="8">
         <v>58</v>
       </c>
       <c r="B63" s="2"/>
@@ -1370,7 +1370,7 @@
       <c r="E63" s="2"/>
     </row>
     <row r="64" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="8">
+      <c r="A64" s="7">
         <v>59</v>
       </c>
       <c r="B64" s="4"/>
@@ -1379,7 +1379,7 @@
       <c r="E64" s="4"/>
     </row>
     <row r="65" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="7">
+      <c r="A65" s="8">
         <v>60</v>
       </c>
       <c r="B65" s="2"/>
@@ -1388,7 +1388,7 @@
       <c r="E65" s="2"/>
     </row>
     <row r="66" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="8">
+      <c r="A66" s="7">
         <v>61</v>
       </c>
       <c r="B66" s="4"/>
@@ -1397,7 +1397,7 @@
       <c r="E66" s="4"/>
     </row>
     <row r="67" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="7">
+      <c r="A67" s="8">
         <v>62</v>
       </c>
       <c r="B67" s="2"/>
@@ -1406,7 +1406,7 @@
       <c r="E67" s="2"/>
     </row>
     <row r="68" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="8">
+      <c r="A68" s="7">
         <v>63</v>
       </c>
       <c r="B68" s="4"/>
@@ -1415,7 +1415,7 @@
       <c r="E68" s="4"/>
     </row>
     <row r="69" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="7">
+      <c r="A69" s="8">
         <v>64</v>
       </c>
       <c r="B69" s="2"/>
@@ -1487,7 +1487,7 @@
       <c r="E76" s="4"/>
     </row>
     <row r="77" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="7">
+      <c r="A77" s="8">
         <v>72</v>
       </c>
       <c r="B77" s="2"/>
@@ -1496,7 +1496,7 @@
       <c r="E77" s="2"/>
     </row>
     <row r="78" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="8">
+      <c r="A78" s="7">
         <v>73</v>
       </c>
       <c r="B78" s="4"/>
@@ -1505,7 +1505,7 @@
       <c r="E78" s="4"/>
     </row>
     <row r="79" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="7">
+      <c r="A79" s="8">
         <v>74</v>
       </c>
       <c r="B79" s="2"/>
@@ -1514,7 +1514,7 @@
       <c r="E79" s="2"/>
     </row>
     <row r="80" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="8">
+      <c r="A80" s="7">
         <v>75</v>
       </c>
       <c r="B80" s="4"/>
@@ -1523,7 +1523,7 @@
       <c r="E80" s="4"/>
     </row>
     <row r="81" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="7">
+      <c r="A81" s="8">
         <v>76</v>
       </c>
       <c r="B81" s="2"/>
@@ -1532,7 +1532,7 @@
       <c r="E81" s="2"/>
     </row>
     <row r="82" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="8">
+      <c r="A82" s="7">
         <v>77</v>
       </c>
       <c r="B82" s="4"/>
@@ -1541,7 +1541,7 @@
       <c r="E82" s="4"/>
     </row>
     <row r="83" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="7">
+      <c r="A83" s="8">
         <v>78</v>
       </c>
       <c r="B83" s="2"/>
